--- a/Project/data/Data/4_China_Imports_YoY.xlsx
+++ b/Project/data/Data/4_China_Imports_YoY.xlsx
@@ -1,20 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karry/KarryRen/Fintech/Karry-PHBS/FintechClass/Class/M2/Financial-Market-and-Investment-in-China/FMIC/Project/data/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12FCEDE-7680-4A42-9B40-7CEA5C439041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="630" windowWidth="27495" windowHeight="13950"/>
+    <workbookView xWindow="640" yWindow="740" windowWidth="27500" windowHeight="13960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="China_Imports_YoY" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$C$2:$C$189</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$C$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$D$2:$D$189</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$C$1</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$C$1:$D$1</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$C$2:$C$189</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$D$2:$D$189</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$C$1</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$C$2:$C$189</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$C$2:$C$189</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$D$2:$D$189</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Sheet2!$B$1:$B$188</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$D$2:$D$189</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$C$2:$C$189</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$D$2:$D$189</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$D$2:$D$189</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$C$1</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$C$2:$C$189</definedName>
+  </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>China: Imports: YoY</t>
   </si>
@@ -43,26 +75,35 @@
     <t>Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Pre</t>
+  </si>
+  <si>
+    <t>Pre-2015 Policy</t>
+  </si>
+  <si>
+    <t>Post-2015 Policy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -71,7 +112,7 @@
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -103,16 +144,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -125,8 +166,707 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.14</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.16</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{AFF0DA3D-1929-6F42-A35E-C3E2E86A4689}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.12</cx:f>
+              <cx:v>Pre-2015 Policy</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{E539D6BD-88C6-304A-B645-72D12524CA8D}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.15</cx:f>
+              <cx:v>Post-2015 Policy</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>607786</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>107043</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>798286</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>183243</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Chart 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2AAFE7A-D809-744A-8B01-FB04BE764BBF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3810000" y="678543"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -172,7 +912,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -205,9 +945,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -240,6 +997,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -415,14 +1189,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H300"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="8" width="13.375" customWidth="1"/>
+    <col min="1" max="8" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -448,7 +1222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>36556</v>
       </c>
@@ -474,7 +1248,7 @@
         <v>3.3242880000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>36585</v>
       </c>
@@ -500,7 +1274,7 @@
         <v>-40.519137999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>36616</v>
       </c>
@@ -526,7 +1300,7 @@
         <v>424.26966299999998</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>36646</v>
       </c>
@@ -552,7 +1326,7 @@
         <v>125.02606900000001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>36677</v>
       </c>
@@ -578,7 +1352,7 @@
         <v>68.739946000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>36707</v>
       </c>
@@ -604,7 +1378,7 @@
         <v>140.22698600000001</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>36738</v>
       </c>
@@ -630,7 +1404,7 @@
         <v>-41.576006999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>36769</v>
       </c>
@@ -656,7 +1430,7 @@
         <v>-47.897435999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>36799</v>
       </c>
@@ -682,7 +1456,7 @@
         <v>-31.418203999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>36830</v>
       </c>
@@ -708,7 +1482,7 @@
         <v>-13.767462999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>36860</v>
       </c>
@@ -734,7 +1508,7 @@
         <v>-80.295950000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>36891</v>
       </c>
@@ -760,7 +1534,7 @@
         <v>-79.694710999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>36922</v>
       </c>
@@ -786,7 +1560,7 @@
         <v>-18.319106999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>36950</v>
       </c>
@@ -812,7 +1586,7 @@
         <v>-45.414200999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>36981</v>
       </c>
@@ -838,7 +1612,7 @@
         <v>-2.9147020000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>37011</v>
       </c>
@@ -864,7 +1638,7 @@
         <v>-57.367933000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>37042</v>
       </c>
@@ -890,7 +1664,7 @@
         <v>-36.510962999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>37072</v>
       </c>
@@ -916,7 +1690,7 @@
         <v>-58.110236</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>37103</v>
       </c>
@@ -942,7 +1716,7 @@
         <v>-6.441872</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>37134</v>
       </c>
@@ -968,7 +1742,7 @@
         <v>-46.417323000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>37164</v>
       </c>
@@ -994,7 +1768,7 @@
         <v>-5.5555560000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>37195</v>
       </c>
@@ -1020,7 +1794,7 @@
         <v>1.6200680000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>37225</v>
       </c>
@@ -1046,7 +1820,7 @@
         <v>523.517787</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>37256</v>
       </c>
@@ -1072,7 +1846,7 @@
         <v>269.40559400000001</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>37287</v>
       </c>
@@ -1098,7 +1872,7 @@
         <v>119.694534</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>37315</v>
       </c>
@@ -1124,7 +1898,7 @@
         <v>337.26287300000001</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>37346</v>
       </c>
@@ -1150,7 +1924,7 @@
         <v>-42.119205000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>37376</v>
       </c>
@@ -1176,7 +1950,7 @@
         <v>6.5217390000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>37407</v>
       </c>
@@ -1202,7 +1976,7 @@
         <v>10.560561</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>37437</v>
       </c>
@@ -1228,7 +2002,7 @@
         <v>265.91478699999999</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>37468</v>
       </c>
@@ -1254,7 +2028,7 @@
         <v>19.419042000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>37499</v>
       </c>
@@ -1280,7 +2054,7 @@
         <v>61.645848999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>37529</v>
       </c>
@@ -1306,7 +2080,7 @@
         <v>-1.1671339999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>37560</v>
       </c>
@@ -1332,7 +2106,7 @@
         <v>22.036512999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>37590</v>
       </c>
@@ -1358,7 +2132,7 @@
         <v>-21.838352</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>37621</v>
       </c>
@@ -1384,7 +2158,7 @@
         <v>49.455750000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37652</v>
       </c>
@@ -1410,7 +2184,7 @@
         <v>-145.371387</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37680</v>
       </c>
@@ -1436,7 +2210,7 @@
         <v>-79.051750999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>37711</v>
       </c>
@@ -1462,7 +2236,7 @@
         <v>-134.93516399999999</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37741</v>
       </c>
@@ -1488,7 +2262,7 @@
         <v>3.4693879999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>37772</v>
       </c>
@@ -1514,7 +2288,7 @@
         <v>0.95065599999999995</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>37802</v>
       </c>
@@ -1540,7 +2314,7 @@
         <v>-26.712329</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>37833</v>
       </c>
@@ -1566,7 +2340,7 @@
         <v>-28.108108000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>37864</v>
       </c>
@@ -1592,7 +2366,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>37894</v>
       </c>
@@ -1618,7 +2392,7 @@
         <v>-86.301370000000006</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>37925</v>
       </c>
@@ -1644,7 +2418,7 @@
         <v>20.817530999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>37955</v>
       </c>
@@ -1670,7 +2444,7 @@
         <v>97.445255000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>37986</v>
       </c>
@@ -1696,7 +2470,7 @@
         <v>81.127296000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>38017</v>
       </c>
@@ -1722,7 +2496,7 @@
         <v>98.145161000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>38046</v>
       </c>
@@ -1748,7 +2522,7 @@
         <v>-1264.4970410000001</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>38077</v>
       </c>
@@ -1774,7 +2548,7 @@
         <v>-17.903929999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>38107</v>
       </c>
@@ -1800,7 +2574,7 @@
         <v>-322.38658800000002</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>38138</v>
       </c>
@@ -1826,7 +2600,7 @@
         <v>-5.6502239999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>38168</v>
       </c>
@@ -1852,7 +2626,7 @@
         <v>-13.878505000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>38199</v>
       </c>
@@ -1878,7 +2652,7 @@
         <v>27.380952000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>38230</v>
       </c>
@@ -1904,7 +2678,7 @@
         <v>60.701503000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>38260</v>
       </c>
@@ -1930,7 +2704,7 @@
         <v>1621.37931</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>38291</v>
       </c>
@@ -1956,7 +2730,7 @@
         <v>23.700731999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>38321</v>
       </c>
@@ -1982,7 +2756,7 @@
         <v>103.224481</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>38352</v>
       </c>
@@ -2008,7 +2782,7 @@
         <v>93.636364</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>38383</v>
       </c>
@@ -2034,7 +2808,7 @@
         <v>28334.782609000002</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>38411</v>
       </c>
@@ -2060,7 +2834,7 @@
         <v>155.34806900000001</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>38442</v>
       </c>
@@ -2086,7 +2860,7 @@
         <v>1161.666667</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>38472</v>
       </c>
@@ -2112,7 +2886,7 @@
         <v>303.592018</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>38503</v>
       </c>
@@ -2138,7 +2912,7 @@
         <v>327.18631199999999</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>38533</v>
       </c>
@@ -2164,7 +2938,7 @@
         <v>425.12208399999997</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>38564</v>
       </c>
@@ -2190,7 +2964,7 @@
         <v>418.69158900000002</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>38595</v>
       </c>
@@ -2216,7 +2990,7 @@
         <v>135.92427599999999</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>38625</v>
       </c>
@@ -2242,7 +3016,7 @@
         <v>51.642628000000002</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>38656</v>
       </c>
@@ -2268,7 +3042,7 @@
         <v>69.406457000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>38686</v>
       </c>
@@ -2294,7 +3068,7 @@
         <v>6.4274889999999996</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>38717</v>
       </c>
@@ -2320,7 +3094,7 @@
         <v>-0.59588300000000005</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>38748</v>
       </c>
@@ -2346,7 +3120,7 @@
         <v>46.165691000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>38776</v>
       </c>
@@ -2372,7 +3146,7 @@
         <v>-44.365389</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>38807</v>
       </c>
@@ -2398,7 +3172,7 @@
         <v>95.168323999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>38837</v>
       </c>
@@ -2424,7 +3198,7 @@
         <v>127.771727</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>38868</v>
       </c>
@@ -2450,7 +3224,7 @@
         <v>44.681798000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>38898</v>
       </c>
@@ -2476,7 +3250,7 @@
         <v>49.855342</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>38929</v>
       </c>
@@ -2502,7 +3276,7 @@
         <v>38.672356999999998</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>38960</v>
       </c>
@@ -2528,7 +3302,7 @@
         <v>77.437931000000006</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>38990</v>
       </c>
@@ -2554,7 +3328,7 @@
         <v>102.113606</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>39021</v>
       </c>
@@ -2580,7 +3354,7 @@
         <v>98.310586000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>39051</v>
       </c>
@@ -2606,7 +3380,7 @@
         <v>117.719115</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>39082</v>
       </c>
@@ -2632,7 +3406,7 @@
         <v>90.708447000000007</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>39113</v>
       </c>
@@ -2658,7 +3432,7 @@
         <v>67.172355999999994</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>39141</v>
       </c>
@@ -2684,7 +3458,7 @@
         <v>881.47689800000001</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>39172</v>
       </c>
@@ -2710,7 +3484,7 @@
         <v>-38.421664</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>39202</v>
       </c>
@@ -2736,7 +3510,7 @@
         <v>60.026775999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>39233</v>
       </c>
@@ -2762,7 +3536,7 @@
         <v>72.485388999999998</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>39263</v>
       </c>
@@ -2788,7 +3562,7 @@
         <v>85.651245000000003</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>39294</v>
       </c>
@@ -2814,7 +3588,7 @@
         <v>67.428023999999994</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>39325</v>
       </c>
@@ -2840,7 +3614,7 @@
         <v>34.071078999999997</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>39355</v>
       </c>
@@ -2866,7 +3640,7 @@
         <v>57.437908</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>39386</v>
       </c>
@@ -2892,7 +3666,7 @@
         <v>14.138235</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>39416</v>
       </c>
@@ -2918,7 +3692,7 @@
         <v>15.095079999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>39447</v>
       </c>
@@ -2944,7 +3718,7 @@
         <v>8.0582940000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>39478</v>
       </c>
@@ -2970,7 +3744,7 @@
         <v>22.731283000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>39507</v>
       </c>
@@ -2996,7 +3770,7 @@
         <v>-65.470135999999997</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>39538</v>
       </c>
@@ -3022,7 +3796,7 @@
         <v>90.609578999999997</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>39568</v>
       </c>
@@ -3048,7 +3822,7 @@
         <v>-0.73502999999999996</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>39599</v>
       </c>
@@ -3074,7 +3848,7 @@
         <v>-11.199287</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>39629</v>
       </c>
@@ -3100,7 +3874,7 @@
         <v>-22.473538000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>39660</v>
       </c>
@@ -3126,7 +3900,7 @@
         <v>3.8475679999999999</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>39691</v>
       </c>
@@ -3152,7 +3926,7 @@
         <v>16.619047999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>39721</v>
       </c>
@@ -3178,7 +3952,7 @@
         <v>24.406343</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>39752</v>
       </c>
@@ -3204,7 +3978,7 @@
         <v>31.568498000000002</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>39782</v>
       </c>
@@ -3230,7 +4004,7 @@
         <v>52.821250999999997</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>39813</v>
       </c>
@@ -3256,7 +4030,7 @@
         <v>71.929129000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>39844</v>
       </c>
@@ -3282,7 +4056,7 @@
         <v>100.83696999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>39872</v>
       </c>
@@ -3308,7 +4082,7 @@
         <v>-41.485087999999998</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>39903</v>
       </c>
@@ -3334,7 +4108,7 @@
         <v>39.861418</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>39933</v>
       </c>
@@ -3360,7 +4134,7 @@
         <v>-22.099813000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>39964</v>
       </c>
@@ -3386,7 +4160,7 @@
         <v>-34.561703000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>39994</v>
       </c>
@@ -3412,7 +4186,7 @@
         <v>-61.928714999999997</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>40025</v>
       </c>
@@ -3438,7 +4212,7 @@
         <v>-59.724679999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>40056</v>
       </c>
@@ -3464,7 +4238,7 @@
         <v>-47.529603999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>40086</v>
       </c>
@@ -3490,7 +4264,7 @@
         <v>-57.733507000000003</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>40117</v>
       </c>
@@ -3516,7 +4290,7 @@
         <v>-33.506594999999997</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>40147</v>
       </c>
@@ -3542,7 +4316,7 @@
         <v>-52.965680999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>40178</v>
       </c>
@@ -3568,7 +4342,7 @@
         <v>-52.854469000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>40209</v>
       </c>
@@ -3594,7 +4368,7 @@
         <v>-64.308542000000003</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>40237</v>
       </c>
@@ -3620,7 +4394,7 @@
         <v>52.631579000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>40268</v>
       </c>
@@ -3646,7 +4420,7 @@
         <v>-140.33100999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>40298</v>
       </c>
@@ -3672,7 +4446,7 @@
         <v>-89.103555</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>40329</v>
       </c>
@@ -3698,7 +4472,7 @@
         <v>49.217430999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>40359</v>
       </c>
@@ -3724,7 +4498,7 @@
         <v>154.007802</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>40390</v>
       </c>
@@ -3750,7 +4524,7 @@
         <v>178.75</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>40421</v>
       </c>
@@ -3776,7 +4550,7 @@
         <v>28.119326000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>40451</v>
       </c>
@@ -3802,7 +4576,7 @@
         <v>30.767409000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>40482</v>
       </c>
@@ -3828,7 +4602,7 @@
         <v>12.658652999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>40512</v>
       </c>
@@ -3854,7 +4628,7 @@
         <v>17.534794999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>40543</v>
       </c>
@@ -3880,7 +4654,7 @@
         <v>-31.444728000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>40574</v>
       </c>
@@ -3906,7 +4680,7 @@
         <v>-58.581662000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>40602</v>
       </c>
@@ -3932,7 +4706,7 @@
         <v>-207.30543800000001</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>40633</v>
       </c>
@@ -3958,7 +4732,7 @@
         <v>97.435204999999996</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>40663</v>
       </c>
@@ -3984,7 +4758,7 @@
         <v>695.88652500000001</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>40694</v>
       </c>
@@ -4010,7 +4784,7 @@
         <v>-33.523574000000004</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>40724</v>
       </c>
@@ -4036,7 +4810,7 @@
         <v>9.9425340000000002</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>40755</v>
       </c>
@@ -4062,7 +4836,7 @@
         <v>5.5773539999999997</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>40786</v>
       </c>
@@ -4088,7 +4862,7 @@
         <v>-9.6223930000000006</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>40816</v>
       </c>
@@ -4114,7 +4888,7 @@
         <v>-11.936242999999999</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>40847</v>
       </c>
@@ -4140,7 +4914,7 @@
         <v>-36.081474</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>40877</v>
       </c>
@@ -4166,7 +4940,7 @@
         <v>-34.224454999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>40908</v>
       </c>
@@ -4192,7 +4966,7 @@
         <v>30.552029999999998</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>40939</v>
       </c>
@@ -4218,7 +4992,7 @@
         <v>367.20857799999999</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>40968</v>
       </c>
@@ -4244,7 +5018,7 @@
         <v>-306.47783600000002</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>40999</v>
       </c>
@@ -4270,7 +5044,7 @@
         <v>2827.8947370000001</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>41029</v>
       </c>
@@ -4296,7 +5070,7 @@
         <v>65.344858000000002</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>41060</v>
       </c>
@@ -4322,7 +5096,7 @@
         <v>40.652796000000002</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>41090</v>
       </c>
@@ -4348,7 +5122,7 @@
         <v>42.608029999999999</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>41121</v>
       </c>
@@ -4374,7 +5148,7 @@
         <v>-16.043934</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>41152</v>
       </c>
@@ -4400,7 +5174,7 @@
         <v>47.958554999999997</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>41182</v>
       </c>
@@ -4426,7 +5200,7 @@
         <v>88.290141000000006</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>41213</v>
       </c>
@@ -4452,7 +5226,7 @@
         <v>87.171705000000003</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>41243</v>
       </c>
@@ -4478,7 +5252,7 @@
         <v>32.849153999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>41274</v>
       </c>
@@ -4504,7 +5278,7 @@
         <v>88.280680000000004</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>41305</v>
       </c>
@@ -4530,7 +5304,7 @@
         <v>3.9794179999999999</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>41333</v>
       </c>
@@ -4556,7 +5330,7 @@
         <v>146.50646800000001</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>41364</v>
       </c>
@@ -4582,7 +5356,7 @@
         <v>-117.48022400000001</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>41394</v>
       </c>
@@ -4608,7 +5382,7 @@
         <v>-1.040151</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>41425</v>
       </c>
@@ -4634,7 +5408,7 @@
         <v>13.604619</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>41455</v>
       </c>
@@ -4660,7 +5434,7 @@
         <v>-13.845618999999999</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>41486</v>
       </c>
@@ -4686,7 +5460,7 @@
         <v>-29.813051000000002</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>41517</v>
       </c>
@@ -4712,7 +5486,7 @@
         <v>6.4917860000000003</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>41547</v>
       </c>
@@ -4738,7 +5512,7 @@
         <v>-46.282406000000002</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>41578</v>
       </c>
@@ -4764,7 +5538,7 @@
         <v>-3.2273149999999999</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>41608</v>
       </c>
@@ -4790,7 +5564,7 @@
         <v>73.261126000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>41639</v>
       </c>
@@ -4816,7 +5590,7 @@
         <v>-18.592495</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>41670</v>
       </c>
@@ -4842,7 +5616,7 @@
         <v>14.004272</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>41698</v>
       </c>
@@ -4868,7 +5642,7 @@
         <v>-251.64261200000001</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>41729</v>
       </c>
@@ -4894,7 +5668,7 @@
         <v>981.30794700000001</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>41759</v>
       </c>
@@ -4920,7 +5694,7 @@
         <v>1.642849</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>41790</v>
       </c>
@@ -4946,7 +5720,7 @@
         <v>75.416961000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>41820</v>
       </c>
@@ -4972,7 +5746,7 @@
         <v>16.969854000000002</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>41851</v>
       </c>
@@ -4998,7 +5772,7 @@
         <v>166.65722500000001</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>41882</v>
       </c>
@@ -5024,7 +5798,7 @@
         <v>77.286886999999993</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>41912</v>
       </c>
@@ -5050,7 +5824,7 @@
         <v>111.57262900000001</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>41943</v>
       </c>
@@ -5076,7 +5850,7 @@
         <v>47.251136000000002</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>41973</v>
       </c>
@@ -5102,7 +5876,7 @@
         <v>62.250940999999997</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>42004</v>
       </c>
@@ -5128,7 +5902,7 @@
         <v>97.852153999999999</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>42035</v>
       </c>
@@ -5154,7 +5928,7 @@
         <v>85.227523000000005</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>42063</v>
       </c>
@@ -5180,7 +5954,7 @@
         <v>367.89924400000001</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>42094</v>
       </c>
@@ -5206,7 +5980,7 @@
         <v>-68.489037999999994</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>42124</v>
       </c>
@@ -5232,7 +6006,7 @@
         <v>77.893992999999995</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>42155</v>
       </c>
@@ -5258,7 +6032,7 @@
         <v>57.713940999999998</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>42185</v>
       </c>
@@ -5284,7 +6058,7 @@
         <v>41.712890000000002</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>42216</v>
       </c>
@@ -5310,7 +6084,7 @@
         <v>-11.579986999999999</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>42247</v>
       </c>
@@ -5336,7 +6110,7 @@
         <v>19.672882000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>42277</v>
       </c>
@@ -5362,7 +6136,7 @@
         <v>90.961933000000002</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>42308</v>
       </c>
@@ -5388,7 +6162,7 @@
         <v>34.107326</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>42338</v>
       </c>
@@ -5414,7 +6188,7 @@
         <v>-1.4390149999999999</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>42369</v>
       </c>
@@ -5440,7 +6214,7 @@
         <v>19.461569000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>42400</v>
       </c>
@@ -5466,7 +6240,7 @@
         <v>-4.1520849999999996</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>42429</v>
       </c>
@@ -5492,7 +6266,7 @@
         <v>-53.443463000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>42460</v>
       </c>
@@ -5518,7 +6292,7 @@
         <v>890.06414800000005</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>42490</v>
       </c>
@@ -5544,7 +6318,7 @@
         <v>20.053142000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>42521</v>
       </c>
@@ -5570,7 +6344,7 @@
         <v>-21.541497</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>42551</v>
       </c>
@@ -5596,7 +6370,7 @@
         <v>0.31879600000000002</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>42582</v>
       </c>
@@ -5622,7 +6396,7 @@
         <v>15.470825</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>42613</v>
       </c>
@@ -5648,7 +6422,7 @@
         <v>-16.069459999999999</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>42643</v>
       </c>
@@ -5674,7 +6448,7 @@
         <v>-32.170399000000003</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>42674</v>
       </c>
@@ -5700,7 +6474,7 @@
         <v>-21.409524000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>42704</v>
       </c>
@@ -5726,7 +6500,7 @@
         <v>-20.180192999999999</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>42735</v>
       </c>
@@ -5752,7 +6526,7 @@
         <v>-33.547150000000002</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>42766</v>
       </c>
@@ -5778,7 +6552,7 @@
         <v>-14.379410999999999</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>42794</v>
       </c>
@@ -5804,7 +6578,7 @@
         <v>-138.86097799999999</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>42825</v>
       </c>
@@ -5830,7 +6604,7 @@
         <v>-8.8453379999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>42855</v>
       </c>
@@ -5856,7 +6630,7 @@
         <v>-8.3982030000000005</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>42886</v>
       </c>
@@ -5882,7 +6656,7 @@
         <v>-10.970858</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>42916</v>
       </c>
@@ -5908,7 +6682,7 @@
         <v>-9.0958009999999998</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>42947</v>
       </c>
@@ -5934,7 +6708,7 @@
         <v>-7.2332809999999998</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>42978</v>
       </c>
@@ -5960,7 +6734,7 @@
         <v>-20.062470999999999</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>43008</v>
       </c>
@@ -5986,7 +6760,7 @@
         <v>-32.288240000000002</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>43039</v>
       </c>
@@ -6012,7 +6786,7 @@
         <v>-23.390650999999998</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>43069</v>
       </c>
@@ -6038,7 +6812,7 @@
         <v>-10.795045999999999</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>43100</v>
       </c>
@@ -6064,7 +6838,7 @@
         <v>35.894869999999997</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>43131</v>
       </c>
@@ -6090,7 +6864,7 @@
         <v>-62.366210000000002</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>43159</v>
       </c>
@@ -6116,7 +6890,7 @@
         <v>394.39619699999997</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>43190</v>
       </c>
@@ -6142,7 +6916,7 @@
         <v>-125.516361</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>43220</v>
       </c>
@@ -6168,7 +6942,7 @@
         <v>-28.196209</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>43251</v>
       </c>
@@ -6194,7 +6968,7 @@
         <v>-41.349598</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>43281</v>
       </c>
@@ -6220,7 +6994,7 @@
         <v>-0.75695100000000004</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>43312</v>
       </c>
@@ -6246,7 +7020,7 @@
         <v>-38.711260000000003</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>43343</v>
       </c>
@@ -6272,7 +7046,7 @@
         <v>-34.333016999999998</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>43373</v>
       </c>
@@ -6298,7 +7072,7 @@
         <v>10.545733</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>43404</v>
       </c>
@@ -6324,7 +7098,7 @@
         <v>-10.637145</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>43434</v>
       </c>
@@ -6350,7 +7124,7 @@
         <v>8.9142139999999994</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>43465</v>
       </c>
@@ -6376,7 +7150,7 @@
         <v>5.47818</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>43496</v>
       </c>
@@ -6402,7 +7176,7 @@
         <v>109.279983</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>43524</v>
       </c>
@@ -6428,7 +7202,7 @@
         <v>-90.811700000000002</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>43555</v>
       </c>
@@ -6454,7 +7228,7 @@
         <v>641.37038299999995</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>43585</v>
       </c>
@@ -6480,7 +7254,7 @@
         <v>-50.131594</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>43616</v>
       </c>
@@ -6506,7 +7280,7 @@
         <v>75.720692</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>43646</v>
       </c>
@@ -6532,7 +7306,7 @@
         <v>21.373393</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>43677</v>
       </c>
@@ -6558,7 +7332,7 @@
         <v>60.124417999999999</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>43708</v>
       </c>
@@ -6584,7 +7358,7 @@
         <v>32.015059000000001</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>43738</v>
       </c>
@@ -6610,7 +7384,7 @@
         <v>29.127977999999999</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>43769</v>
       </c>
@@ -6636,7 +7410,7 @@
         <v>28.307151000000001</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>43799</v>
       </c>
@@ -6662,7 +7436,7 @@
         <v>-11.187557999999999</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>43830</v>
       </c>
@@ -6688,7 +7462,7 @@
         <v>-16.816901000000001</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>43861</v>
       </c>
@@ -6714,7 +7488,7 @@
         <v>42.592205999999997</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>43890</v>
       </c>
@@ -6740,7 +7514,7 @@
         <v>-2195.0321049999998</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>43921</v>
       </c>
@@ -6766,7 +7540,7 @@
         <v>-36.337552000000002</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>43951</v>
       </c>
@@ -6792,7 +7566,7 @@
         <v>243.71271200000001</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>43982</v>
       </c>
@@ -6818,7 +7592,7 @@
         <v>49.755741999999998</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>44012</v>
       </c>
@@ -6844,7 +7618,7 @@
         <v>-10.008258</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>44043</v>
       </c>
@@ -6870,7 +7644,7 @@
         <v>37.019198000000003</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>44074</v>
       </c>
@@ -6896,7 +7670,7 @@
         <v>64.480355000000003</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>44104</v>
       </c>
@@ -6922,7 +7696,7 @@
         <v>-9.5552480000000006</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>44135</v>
       </c>
@@ -6948,7 +7722,7 @@
         <v>35.487378</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>44165</v>
       </c>
@@ -6974,7 +7748,7 @@
         <v>99.722939999999994</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>44196</v>
       </c>
@@ -7000,7 +7774,7 @@
         <v>60.408906000000002</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>44227</v>
       </c>
@@ -7026,7 +7800,7 @@
         <v>12.329193</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44255</v>
       </c>
@@ -7052,7 +7826,7 @@
         <v>156.47019</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>44286</v>
       </c>
@@ -7078,7 +7852,7 @@
         <v>-42.150333000000003</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>44316</v>
       </c>
@@ -7104,7 +7878,7 @@
         <v>-9.9339069999999996</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>44347</v>
       </c>
@@ -7130,7 +7904,7 @@
         <v>-30.481847999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>44377</v>
       </c>
@@ -7156,7 +7930,7 @@
         <v>10.651298000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>44408</v>
       </c>
@@ -7182,7 +7956,7 @@
         <v>-9.0682980000000004</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>44439</v>
       </c>
@@ -7208,7 +7982,7 @@
         <v>2.3537240000000001</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>44469</v>
       </c>
@@ -7234,7 +8008,7 @@
         <v>91.084766999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>44500</v>
       </c>
@@ -7260,7 +8034,7 @@
         <v>47.248874999999998</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>44530</v>
       </c>
@@ -7286,7 +8060,7 @@
         <v>-4.0189089999999998</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>44561</v>
       </c>
@@ -7312,7 +8086,7 @@
         <v>22.981923999999999</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>44592</v>
       </c>
@@ -7338,7 +8112,7 @@
         <v>29.148143000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>44620</v>
       </c>
@@ -7364,7 +8138,7 @@
         <v>-25.226382999999998</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>44651</v>
       </c>
@@ -7390,7 +8164,7 @@
         <v>270.95740999999998</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>44681</v>
       </c>
@@ -7416,7 +8190,7 @@
         <v>14.375014999999999</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>44712</v>
       </c>
@@ -7442,7 +8216,7 @@
         <v>77.684137000000007</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>44742</v>
       </c>
@@ -7468,7 +8242,7 @@
         <v>88.731567999999996</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>44773</v>
       </c>
@@ -7494,7 +8268,7 @@
         <v>79.139313999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>44804</v>
       </c>
@@ -7520,7 +8294,7 @@
         <v>31.739242000000001</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>44834</v>
       </c>
@@ -7546,7 +8320,7 @@
         <v>21.638508999999999</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>44865</v>
       </c>
@@ -7572,7 +8346,7 @@
         <v>-3.1976399999999998</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>44895</v>
       </c>
@@ -7598,7 +8372,7 @@
         <v>-7.6896089999999999</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>44926</v>
       </c>
@@ -7624,7 +8398,7 @@
         <v>-25.964509</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>44957</v>
       </c>
@@ -7650,7 +8424,7 @@
         <v>15.832345999999999</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>44985</v>
       </c>
@@ -7676,7 +8450,7 @@
         <v>-54.080072999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>45016</v>
       </c>
@@ -7702,7 +8476,7 @@
         <v>79.854386000000005</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>45046</v>
       </c>
@@ -7728,7 +8502,7 @@
         <v>83.724698000000004</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>45077</v>
       </c>
@@ -7754,7 +8528,7 @@
         <v>-14.398707</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>45107</v>
       </c>
@@ -7780,7 +8554,7 @@
         <v>-25.452538000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>45138</v>
       </c>
@@ -7806,7 +8580,7 @@
         <v>-19.181595999999999</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>45169</v>
       </c>
@@ -7832,7 +8606,7 @@
         <v>-12.696928</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>45199</v>
       </c>
@@ -7858,7 +8632,7 @@
         <v>-8.5586300000000008</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>45230</v>
       </c>
@@ -7884,7 +8658,7 @@
         <v>-31.631316999999999</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>45260</v>
       </c>
@@ -7910,7 +8684,7 @@
         <v>4.9859390000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>45291</v>
       </c>
@@ -7936,7 +8710,7 @@
         <v>8.2890139999999999</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>45322</v>
       </c>
@@ -7962,7 +8736,7 @@
         <v>-8.9079270000000008</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>45351</v>
       </c>
@@ -7988,7 +8762,7 @@
         <v>239.70892699999999</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>45382</v>
       </c>
@@ -8014,7 +8788,7 @@
         <v>-25.523854</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>45412</v>
       </c>
@@ -8040,7 +8814,7 @@
         <v>-16.141473000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>45443</v>
       </c>
@@ -8066,7 +8840,7 @@
         <v>25.257859</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>45473</v>
       </c>
@@ -8092,7 +8866,7 @@
         <v>41.947727</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>45504</v>
       </c>
@@ -8118,7 +8892,7 @@
         <v>7.1288229999999997</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>45535</v>
       </c>
@@ -8144,7 +8918,7 @@
         <v>35.689314000000003</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>45565</v>
       </c>
@@ -8170,7 +8944,7 @@
         <v>8.723376</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>45596</v>
       </c>
@@ -8196,7 +8970,7 @@
         <v>71.341877999999994</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>45626</v>
       </c>
@@ -8226,4 +9000,3151 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B16DBA-8333-6940-8F5B-E7C575BA3B0F}">
+  <dimension ref="A1:E189"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="31.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>42277</v>
+      </c>
+      <c r="C2" s="2">
+        <v>15.23</v>
+      </c>
+      <c r="D2" s="2">
+        <v>596.05539999999996</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>42308</v>
+      </c>
+      <c r="C3" s="2">
+        <v>13.52</v>
+      </c>
+      <c r="D3" s="2">
+        <v>612.8623</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>42338</v>
+      </c>
+      <c r="C4" s="2">
+        <v>23.33</v>
+      </c>
+      <c r="D4" s="2">
+        <v>539.76490000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>42369</v>
+      </c>
+      <c r="C5" s="2">
+        <v>21.58</v>
+      </c>
+      <c r="D5" s="2">
+        <v>596.30579999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>42400</v>
+      </c>
+      <c r="C6" s="2">
+        <v>31.47</v>
+      </c>
+      <c r="D6" s="2">
+        <v>568.51980000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>42429</v>
+      </c>
+      <c r="C7" s="2">
+        <v>19.05</v>
+      </c>
+      <c r="D7" s="2">
+        <v>281.49059999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>42460</v>
+      </c>
+      <c r="C8" s="2">
+        <v>19.87</v>
+      </c>
+      <c r="D8" s="2">
+        <v>249.10409999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>42490</v>
+      </c>
+      <c r="C9" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="D9" s="2">
+        <v>398.59480000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>42521</v>
+      </c>
+      <c r="C10" s="2">
+        <v>22.68</v>
+      </c>
+      <c r="D10" s="2">
+        <v>448.42619999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>42551</v>
+      </c>
+      <c r="C11" s="2">
+        <v>38.270000000000003</v>
+      </c>
+      <c r="D11" s="2">
+        <v>453.42239999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>42582</v>
+      </c>
+      <c r="C12" s="2">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="D12" s="2">
+        <v>483.4708</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>42613</v>
+      </c>
+      <c r="C13" s="2">
+        <v>5.72</v>
+      </c>
+      <c r="D13" s="2">
+        <v>500.96620000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>42643</v>
+      </c>
+      <c r="C14" s="2">
+        <v>12.44</v>
+      </c>
+      <c r="D14" s="2">
+        <v>404.30200000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>42674</v>
+      </c>
+      <c r="C15" s="2">
+        <v>7.38</v>
+      </c>
+      <c r="D15" s="2">
+        <v>481.65140000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>42704</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22.65</v>
+      </c>
+      <c r="D16" s="2">
+        <v>430.83929999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>42735</v>
+      </c>
+      <c r="C17" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D17" s="2">
+        <v>396.26220000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>42766</v>
+      </c>
+      <c r="C18" s="2">
+        <v>19.98</v>
+      </c>
+      <c r="D18" s="2">
+        <v>486.77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>42794</v>
+      </c>
+      <c r="C19" s="2">
+        <v>7.98</v>
+      </c>
+      <c r="D19" s="2">
+        <v>-109.39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>42825</v>
+      </c>
+      <c r="C20" s="2">
+        <v>18.59</v>
+      </c>
+      <c r="D20" s="2">
+        <v>227.07</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>42855</v>
+      </c>
+      <c r="C21" s="2">
+        <v>13.61</v>
+      </c>
+      <c r="D21" s="2">
+        <v>365.12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>42886</v>
+      </c>
+      <c r="C22" s="2">
+        <v>21.42</v>
+      </c>
+      <c r="D22" s="2">
+        <v>399.23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>42916</v>
+      </c>
+      <c r="C23" s="2">
+        <v>38.89</v>
+      </c>
+      <c r="D23" s="2">
+        <v>412.18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>42947</v>
+      </c>
+      <c r="C24" s="2">
+        <v>31.55</v>
+      </c>
+      <c r="D24" s="2">
+        <v>448.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>42978</v>
+      </c>
+      <c r="C25" s="2">
+        <v>21.13</v>
+      </c>
+      <c r="D25" s="2">
+        <v>400.46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>43008</v>
+      </c>
+      <c r="C26" s="2">
+        <v>27.33</v>
+      </c>
+      <c r="D26" s="2">
+        <v>273.76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>43039</v>
+      </c>
+      <c r="C27" s="2">
+        <v>32.270000000000003</v>
+      </c>
+      <c r="D27" s="2">
+        <v>368.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>43069</v>
+      </c>
+      <c r="C28" s="2">
+        <v>13.11</v>
+      </c>
+      <c r="D28" s="2">
+        <v>384.33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>43100</v>
+      </c>
+      <c r="C29" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D29" s="2">
+        <v>538.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>43131</v>
+      </c>
+      <c r="C30" s="2">
+        <v>22.09</v>
+      </c>
+      <c r="D30" s="2">
+        <v>183.19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>43159</v>
+      </c>
+      <c r="C31" s="2">
+        <v>29.2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>322.04000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>43190</v>
+      </c>
+      <c r="C32" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="D32" s="2">
+        <v>-57.94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>43220</v>
+      </c>
+      <c r="C33" s="2">
+        <v>22</v>
+      </c>
+      <c r="D33" s="2">
+        <v>262.17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>43251</v>
+      </c>
+      <c r="C34" s="2">
+        <v>21.17</v>
+      </c>
+      <c r="D34" s="2">
+        <v>234.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>43281</v>
+      </c>
+      <c r="C35" s="2">
+        <v>47.46</v>
+      </c>
+      <c r="D35" s="2">
+        <v>409.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>43312</v>
+      </c>
+      <c r="C36" s="2">
+        <v>24.66</v>
+      </c>
+      <c r="D36" s="2">
+        <v>274.88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>43343</v>
+      </c>
+      <c r="C37" s="2">
+        <v>31.58</v>
+      </c>
+      <c r="D37" s="2">
+        <v>262.97000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>43373</v>
+      </c>
+      <c r="C38" s="2">
+        <v>-12.4</v>
+      </c>
+      <c r="D38" s="2">
+        <v>302.63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>43404</v>
+      </c>
+      <c r="C39" s="2">
+        <v>6.76</v>
+      </c>
+      <c r="D39" s="2">
+        <v>329.74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>43434</v>
+      </c>
+      <c r="C40" s="2">
+        <v>-4.58</v>
+      </c>
+      <c r="D40" s="2">
+        <v>418.59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C41" s="2">
+        <v>10.14</v>
+      </c>
+      <c r="D41" s="2">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>43496</v>
+      </c>
+      <c r="C42" s="2">
+        <v>22.3</v>
+      </c>
+      <c r="D42" s="2">
+        <v>383.38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>43524</v>
+      </c>
+      <c r="C43" s="2">
+        <v>21.4</v>
+      </c>
+      <c r="D43" s="2">
+        <v>29.59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>43555</v>
+      </c>
+      <c r="C44" s="2">
+        <v>15.96</v>
+      </c>
+      <c r="D44" s="2">
+        <v>313.67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>43585</v>
+      </c>
+      <c r="C45" s="2">
+        <v>27.94</v>
+      </c>
+      <c r="D45" s="2">
+        <v>130.74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>43616</v>
+      </c>
+      <c r="C46" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D46" s="2">
+        <v>411.45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>43646</v>
+      </c>
+      <c r="C47" s="2">
+        <v>57.34</v>
+      </c>
+      <c r="D47" s="2">
+        <v>496.49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>43677</v>
+      </c>
+      <c r="C48" s="2">
+        <v>48.69</v>
+      </c>
+      <c r="D48" s="2">
+        <v>440.15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>43708</v>
+      </c>
+      <c r="C49" s="2">
+        <v>57.2</v>
+      </c>
+      <c r="D49" s="2">
+        <v>347.16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>43738</v>
+      </c>
+      <c r="C50" s="2">
+        <v>-0.23</v>
+      </c>
+      <c r="D50" s="2">
+        <v>390.78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>43769</v>
+      </c>
+      <c r="C51" s="2">
+        <v>-78.72</v>
+      </c>
+      <c r="D51" s="2">
+        <v>423.08</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>43799</v>
+      </c>
+      <c r="C52" s="2">
+        <v>-5.4</v>
+      </c>
+      <c r="D52" s="2">
+        <v>371.76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>43830</v>
+      </c>
+      <c r="C53" s="2">
+        <v>-22.55</v>
+      </c>
+      <c r="D53" s="2">
+        <v>472.48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>43861</v>
+      </c>
+      <c r="C54" s="2">
+        <v>21.04</v>
+      </c>
+      <c r="D54" s="2">
+        <v>546.66999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>43890</v>
+      </c>
+      <c r="C55" s="2">
+        <v>18.43</v>
+      </c>
+      <c r="D55" s="2">
+        <v>-619.91999999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>43921</v>
+      </c>
+      <c r="C56" s="2">
+        <v>20.329999999999998</v>
+      </c>
+      <c r="D56" s="2">
+        <v>199.69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>43951</v>
+      </c>
+      <c r="C57" s="2">
+        <v>44.9</v>
+      </c>
+      <c r="D57" s="2">
+        <v>449.37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>43982</v>
+      </c>
+      <c r="C58" s="2">
+        <v>49.92</v>
+      </c>
+      <c r="D58" s="2">
+        <v>616.16999999999996</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>44012</v>
+      </c>
+      <c r="C59" s="2">
+        <v>70.930000000000007</v>
+      </c>
+      <c r="D59" s="2">
+        <v>446.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>44043</v>
+      </c>
+      <c r="C60" s="2">
+        <v>98.95</v>
+      </c>
+      <c r="D60" s="2">
+        <v>603.09</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>44074</v>
+      </c>
+      <c r="C61" s="2">
+        <v>110.76</v>
+      </c>
+      <c r="D61" s="2">
+        <v>571.01</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>44104</v>
+      </c>
+      <c r="C62" s="2">
+        <v>64.94</v>
+      </c>
+      <c r="D62" s="2">
+        <v>353.44</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>44135</v>
+      </c>
+      <c r="C63" s="2">
+        <v>43.57</v>
+      </c>
+      <c r="D63" s="2">
+        <v>573.22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>44165</v>
+      </c>
+      <c r="C64" s="2">
+        <v>57.33</v>
+      </c>
+      <c r="D64" s="2">
+        <v>742.49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>44196</v>
+      </c>
+      <c r="C65" s="2">
+        <v>45.91</v>
+      </c>
+      <c r="D65" s="2">
+        <v>757.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C66" s="2">
+        <v>89.88</v>
+      </c>
+      <c r="D66" s="2">
+        <v>614.07000000000005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>44255</v>
+      </c>
+      <c r="C67" s="2">
+        <v>96.78</v>
+      </c>
+      <c r="D67" s="2">
+        <v>350.07</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>44286</v>
+      </c>
+      <c r="C68" s="2">
+        <v>105.45</v>
+      </c>
+      <c r="D68" s="2">
+        <v>115.52</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>44316</v>
+      </c>
+      <c r="C69" s="2">
+        <v>105.93</v>
+      </c>
+      <c r="D69" s="2">
+        <v>404.73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>44347</v>
+      </c>
+      <c r="C70" s="2">
+        <v>75.7</v>
+      </c>
+      <c r="D70" s="2">
+        <v>428.35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>44377</v>
+      </c>
+      <c r="C71" s="2">
+        <v>120.16</v>
+      </c>
+      <c r="D71" s="2">
+        <v>494.39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>44408</v>
+      </c>
+      <c r="C72" s="2">
+        <v>105.31</v>
+      </c>
+      <c r="D72" s="2">
+        <v>548.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>44439</v>
+      </c>
+      <c r="C73" s="2">
+        <v>110.1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>584.45000000000005</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>44469</v>
+      </c>
+      <c r="C74" s="2">
+        <v>94.92</v>
+      </c>
+      <c r="D74" s="2">
+        <v>675.37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>44500</v>
+      </c>
+      <c r="C75" s="2">
+        <v>24.24</v>
+      </c>
+      <c r="D75" s="2">
+        <v>844.06</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>44530</v>
+      </c>
+      <c r="C76" s="2">
+        <v>111.89</v>
+      </c>
+      <c r="D76" s="2">
+        <v>712.65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>44561</v>
+      </c>
+      <c r="C77" s="2">
+        <v>104.57</v>
+      </c>
+      <c r="D77" s="2">
+        <v>932.08</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>44592</v>
+      </c>
+      <c r="C78" s="2">
+        <v>130.04</v>
+      </c>
+      <c r="D78" s="2">
+        <v>793.06</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>44620</v>
+      </c>
+      <c r="C79" s="2">
+        <v>145.03</v>
+      </c>
+      <c r="D79" s="2">
+        <v>261.76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>44651</v>
+      </c>
+      <c r="C80" s="2">
+        <v>146.22999999999999</v>
+      </c>
+      <c r="D80" s="2">
+        <v>428.53</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C81" s="2">
+        <v>187.96</v>
+      </c>
+      <c r="D81" s="2">
+        <v>462.91</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>44712</v>
+      </c>
+      <c r="C82" s="2">
+        <v>153</v>
+      </c>
+      <c r="D82" s="2">
+        <v>761.11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>44742</v>
+      </c>
+      <c r="C83" s="2">
+        <v>238.29</v>
+      </c>
+      <c r="D83" s="2">
+        <v>933.07</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>44773</v>
+      </c>
+      <c r="C84" s="2">
+        <v>229.28</v>
+      </c>
+      <c r="D84" s="2">
+        <v>982.4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>44804</v>
+      </c>
+      <c r="C85" s="2">
+        <v>209.97</v>
+      </c>
+      <c r="D85" s="2">
+        <v>769.95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>44834</v>
+      </c>
+      <c r="C86" s="2">
+        <v>158.68</v>
+      </c>
+      <c r="D86" s="2">
+        <v>821.51</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>44865</v>
+      </c>
+      <c r="C87" s="2">
+        <v>237.91</v>
+      </c>
+      <c r="D87" s="2">
+        <v>817.07</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>44895</v>
+      </c>
+      <c r="C88" s="2">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="D88" s="2">
+        <v>657.85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>44926</v>
+      </c>
+      <c r="C89" s="2">
+        <v>167.34</v>
+      </c>
+      <c r="D89" s="2">
+        <v>690.07</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>44957</v>
+      </c>
+      <c r="C90" s="2">
+        <v>224.3</v>
+      </c>
+      <c r="D90" s="2">
+        <v>918.62</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>44985</v>
+      </c>
+      <c r="C91" s="2">
+        <v>269.25</v>
+      </c>
+      <c r="D91" s="2">
+        <v>120.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>45016</v>
+      </c>
+      <c r="C92" s="2">
+        <v>244.83</v>
+      </c>
+      <c r="D92" s="2">
+        <v>770.73</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>45046</v>
+      </c>
+      <c r="C93" s="2">
+        <v>252</v>
+      </c>
+      <c r="D93" s="2">
+        <v>850.48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>45077</v>
+      </c>
+      <c r="C94" s="2">
+        <v>240.88</v>
+      </c>
+      <c r="D94" s="2">
+        <v>651.52</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>45107</v>
+      </c>
+      <c r="C95" s="2">
+        <v>271.98</v>
+      </c>
+      <c r="D95" s="2">
+        <v>695.58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>45138</v>
+      </c>
+      <c r="C96" s="2">
+        <v>263.89</v>
+      </c>
+      <c r="D96" s="2">
+        <v>793.96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>45169</v>
+      </c>
+      <c r="C97" s="2">
+        <v>226.89</v>
+      </c>
+      <c r="D97" s="2">
+        <v>672.19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>45199</v>
+      </c>
+      <c r="C98" s="2">
+        <v>194.75</v>
+      </c>
+      <c r="D98" s="2">
+        <v>751.2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>45230</v>
+      </c>
+      <c r="C99" s="2">
+        <v>82.15</v>
+      </c>
+      <c r="D99" s="2">
+        <v>558.62</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>45260</v>
+      </c>
+      <c r="C100" s="2">
+        <v>131.33000000000001</v>
+      </c>
+      <c r="D100" s="2">
+        <v>690.65</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>45291</v>
+      </c>
+      <c r="C101" s="2">
+        <v>166.11</v>
+      </c>
+      <c r="D101" s="2">
+        <v>747.27</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>45322</v>
+      </c>
+      <c r="C102" s="2">
+        <v>199.18</v>
+      </c>
+      <c r="D102" s="2">
+        <v>836.79</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>45351</v>
+      </c>
+      <c r="C103" s="2">
+        <v>208.74</v>
+      </c>
+      <c r="D103" s="2">
+        <v>408.33013</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>45382</v>
+      </c>
+      <c r="C104" s="2">
+        <v>254.25</v>
+      </c>
+      <c r="D104" s="2">
+        <v>574.01</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>45412</v>
+      </c>
+      <c r="C105" s="2">
+        <v>293.88</v>
+      </c>
+      <c r="D105" s="2">
+        <v>713.2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>45443</v>
+      </c>
+      <c r="C106" s="2">
+        <v>299.67</v>
+      </c>
+      <c r="D106" s="2">
+        <v>816.08</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>45473</v>
+      </c>
+      <c r="C107" s="2">
+        <v>357.84</v>
+      </c>
+      <c r="D107" s="2">
+        <v>987.36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>45504</v>
+      </c>
+      <c r="C108" s="2">
+        <v>403.28</v>
+      </c>
+      <c r="D108" s="2">
+        <v>850.56</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>45535</v>
+      </c>
+      <c r="C109" s="2">
+        <v>390.09</v>
+      </c>
+      <c r="D109" s="2">
+        <v>912.09</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>45565</v>
+      </c>
+      <c r="C110" s="2">
+        <v>391.13</v>
+      </c>
+      <c r="D110" s="2">
+        <v>816.73</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>45596</v>
+      </c>
+      <c r="C111" s="2">
+        <v>48.07</v>
+      </c>
+      <c r="D111" s="2">
+        <v>957.15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>45626</v>
+      </c>
+      <c r="C112" s="2">
+        <v>183.68</v>
+      </c>
+      <c r="D112" s="2">
+        <v>974.43</v>
+      </c>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C113" s="2">
+        <v>129.4</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C114" s="2">
+        <v>130.34</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C115" s="2">
+        <v>79.47</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C116" s="2">
+        <v>102.4</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C117" s="2">
+        <v>154.19999999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C118" s="2">
+        <v>126.66</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C119" s="2">
+        <v>237.94</v>
+      </c>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C120" s="2">
+        <v>189.68</v>
+      </c>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C121" s="2">
+        <v>183.91</v>
+      </c>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C122" s="2">
+        <v>139.6</v>
+      </c>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C123" s="2">
+        <v>73.37</v>
+      </c>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C124" s="2">
+        <v>-74.08</v>
+      </c>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C125" s="2">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C126" s="2">
+        <v>194.49</v>
+      </c>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C127" s="2">
+        <v>201.86</v>
+      </c>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C128" s="2">
+        <v>285.44</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C129" s="2">
+        <v>197.56</v>
+      </c>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C130" s="2">
+        <v>165.63</v>
+      </c>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C131" s="2">
+        <v>268.06</v>
+      </c>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C132" s="2">
+        <v>222.94</v>
+      </c>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C133" s="2">
+        <v>126.08</v>
+      </c>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C134" s="2">
+        <v>57.82</v>
+      </c>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C135" s="2">
+        <v>-78.73</v>
+      </c>
+    </row>
+    <row r="136" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C136" s="2">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="137" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C137" s="2">
+        <v>112.22</v>
+      </c>
+    </row>
+    <row r="138" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C138" s="2">
+        <v>129.29</v>
+      </c>
+    </row>
+    <row r="139" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C139" s="2">
+        <v>221.93</v>
+      </c>
+    </row>
+    <row r="140" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C140" s="2">
+        <v>301.36</v>
+      </c>
+    </row>
+    <row r="141" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C141" s="2">
+        <v>178.55</v>
+      </c>
+    </row>
+    <row r="142" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C142" s="2">
+        <v>145.86000000000001</v>
+      </c>
+    </row>
+    <row r="143" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C143" s="2">
+        <v>171.34</v>
+      </c>
+    </row>
+    <row r="144" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C144" s="2">
+        <v>146.63999999999999</v>
+      </c>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C145" s="2">
+        <v>164.6</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C146" s="2">
+        <v>270.14</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C147" s="2">
+        <v>-320.02</v>
+      </c>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C148" s="2">
+        <v>51.83</v>
+      </c>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C149" s="2">
+        <v>185.55</v>
+      </c>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C150" s="2">
+        <v>181.85</v>
+      </c>
+    </row>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C151" s="2">
+        <v>316.49</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C152" s="2">
+        <v>253.01</v>
+      </c>
+    </row>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C153" s="2">
+        <v>264.18</v>
+      </c>
+    </row>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C154" s="2">
+        <v>274.64</v>
+      </c>
+    </row>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C155" s="2">
+        <v>320.7</v>
+      </c>
+    </row>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C156" s="2">
+        <v>194.81</v>
+      </c>
+    </row>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C157" s="2">
+        <v>309.91000000000003</v>
+      </c>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C158" s="2">
+        <v>280.89</v>
+      </c>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C159" s="2">
+        <v>148.83000000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C160" s="2">
+        <v>-9.06</v>
+      </c>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C161" s="2">
+        <v>183.62</v>
+      </c>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C162" s="2">
+        <v>206.59</v>
+      </c>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C163" s="2">
+        <v>272.67</v>
+      </c>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C164" s="2">
+        <v>177.58</v>
+      </c>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C165" s="2">
+        <v>281.33</v>
+      </c>
+    </row>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C166" s="2">
+        <v>147.53</v>
+      </c>
+    </row>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C167" s="2">
+        <v>310.35000000000002</v>
+      </c>
+    </row>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C168" s="2">
+        <v>337.53</v>
+      </c>
+    </row>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C169" s="2">
+        <v>252.29</v>
+      </c>
+    </row>
+    <row r="170" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C170" s="2">
+        <v>320.22660000000002</v>
+      </c>
+    </row>
+    <row r="171" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C171" s="2">
+        <v>-225.68969999999999</v>
+      </c>
+    </row>
+    <row r="172" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C172" s="2">
+        <v>79.846500000000006</v>
+      </c>
+    </row>
+    <row r="173" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C173" s="2">
+        <v>186.63659999999999</v>
+      </c>
+    </row>
+    <row r="174" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C174" s="2">
+        <v>362.39389999999997</v>
+      </c>
+    </row>
+    <row r="175" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C175" s="2">
+        <v>318.94170000000003</v>
+      </c>
+    </row>
+    <row r="176" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C176" s="2">
+        <v>473.5299</v>
+      </c>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C177" s="2">
+        <v>498.76119999999997</v>
+      </c>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C178" s="2">
+        <v>312.13310000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C179" s="2">
+        <v>456.9939</v>
+      </c>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C180" s="2">
+        <v>547.64559999999994</v>
+      </c>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C181" s="2">
+        <v>499.16120000000001</v>
+      </c>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C182" s="2">
+        <v>593.14779999999996</v>
+      </c>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C183" s="2">
+        <v>604.62099999999998</v>
+      </c>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C184" s="2">
+        <v>25.160399999999999</v>
+      </c>
+    </row>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C185" s="2">
+        <v>332.01530000000002</v>
+      </c>
+    </row>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C186" s="2">
+        <v>571.54570000000001</v>
+      </c>
+    </row>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C187" s="2">
+        <v>451.98149999999998</v>
+      </c>
+    </row>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C188" s="2">
+        <v>418.6952</v>
+      </c>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C189" s="2">
+        <v>596.88189999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89B869F-AE86-794A-A22C-4D48E04C384D}">
+  <dimension ref="A1:B188"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1">
+        <v>36556</v>
+      </c>
+      <c r="B1" s="2">
+        <v>15.23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>36585</v>
+      </c>
+      <c r="B2" s="2">
+        <v>13.52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>36616</v>
+      </c>
+      <c r="B3" s="2">
+        <v>23.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>36646</v>
+      </c>
+      <c r="B4" s="2">
+        <v>21.58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>36677</v>
+      </c>
+      <c r="B5" s="2">
+        <v>31.47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>36707</v>
+      </c>
+      <c r="B6" s="2">
+        <v>19.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>36738</v>
+      </c>
+      <c r="B7" s="2">
+        <v>19.87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>36769</v>
+      </c>
+      <c r="B8" s="2">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>36799</v>
+      </c>
+      <c r="B9" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>36830</v>
+      </c>
+      <c r="B10" s="2">
+        <v>38.270000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>36860</v>
+      </c>
+      <c r="B11" s="2">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>36891</v>
+      </c>
+      <c r="B12" s="2">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>36922</v>
+      </c>
+      <c r="B13" s="2">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>36950</v>
+      </c>
+      <c r="B14" s="2">
+        <v>7.38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>36981</v>
+      </c>
+      <c r="B15" s="2">
+        <v>22.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>37011</v>
+      </c>
+      <c r="B16" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>37042</v>
+      </c>
+      <c r="B17" s="2">
+        <v>19.98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>37072</v>
+      </c>
+      <c r="B18" s="2">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>37103</v>
+      </c>
+      <c r="B19" s="2">
+        <v>18.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>37134</v>
+      </c>
+      <c r="B20" s="2">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>37164</v>
+      </c>
+      <c r="B21" s="2">
+        <v>21.42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>37195</v>
+      </c>
+      <c r="B22" s="2">
+        <v>38.89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>37225</v>
+      </c>
+      <c r="B23" s="2">
+        <v>31.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>37256</v>
+      </c>
+      <c r="B24" s="2">
+        <v>21.13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>37287</v>
+      </c>
+      <c r="B25" s="2">
+        <v>27.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>37315</v>
+      </c>
+      <c r="B26" s="2">
+        <v>32.270000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>37346</v>
+      </c>
+      <c r="B27" s="2">
+        <v>13.11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>37376</v>
+      </c>
+      <c r="B28" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>37407</v>
+      </c>
+      <c r="B29" s="2">
+        <v>22.09</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>37437</v>
+      </c>
+      <c r="B30" s="2">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>37468</v>
+      </c>
+      <c r="B31" s="2">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>37499</v>
+      </c>
+      <c r="B32" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>37529</v>
+      </c>
+      <c r="B33" s="2">
+        <v>21.17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>37560</v>
+      </c>
+      <c r="B34" s="2">
+        <v>47.46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>37590</v>
+      </c>
+      <c r="B35" s="2">
+        <v>24.66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>37621</v>
+      </c>
+      <c r="B36" s="2">
+        <v>31.58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>37652</v>
+      </c>
+      <c r="B37" s="2">
+        <v>-12.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37680</v>
+      </c>
+      <c r="B38" s="2">
+        <v>6.76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>37711</v>
+      </c>
+      <c r="B39" s="2">
+        <v>-4.58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>37741</v>
+      </c>
+      <c r="B40" s="2">
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>37772</v>
+      </c>
+      <c r="B41" s="2">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>37802</v>
+      </c>
+      <c r="B42" s="2">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>37833</v>
+      </c>
+      <c r="B43" s="2">
+        <v>15.96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>37864</v>
+      </c>
+      <c r="B44" s="2">
+        <v>27.94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>37894</v>
+      </c>
+      <c r="B45" s="2">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>37925</v>
+      </c>
+      <c r="B46" s="2">
+        <v>57.34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>37955</v>
+      </c>
+      <c r="B47" s="2">
+        <v>48.69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>37986</v>
+      </c>
+      <c r="B48" s="2">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>38017</v>
+      </c>
+      <c r="B49" s="2">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>38046</v>
+      </c>
+      <c r="B50" s="2">
+        <v>-78.72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>38077</v>
+      </c>
+      <c r="B51" s="2">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>38107</v>
+      </c>
+      <c r="B52" s="2">
+        <v>-22.55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>38138</v>
+      </c>
+      <c r="B53" s="2">
+        <v>21.04</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>38168</v>
+      </c>
+      <c r="B54" s="2">
+        <v>18.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>38199</v>
+      </c>
+      <c r="B55" s="2">
+        <v>20.329999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>38230</v>
+      </c>
+      <c r="B56" s="2">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>38260</v>
+      </c>
+      <c r="B57" s="2">
+        <v>49.92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>38291</v>
+      </c>
+      <c r="B58" s="2">
+        <v>70.930000000000007</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>38321</v>
+      </c>
+      <c r="B59" s="2">
+        <v>98.95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>38352</v>
+      </c>
+      <c r="B60" s="2">
+        <v>110.76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>38383</v>
+      </c>
+      <c r="B61" s="2">
+        <v>64.94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>38411</v>
+      </c>
+      <c r="B62" s="2">
+        <v>43.57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>38442</v>
+      </c>
+      <c r="B63" s="2">
+        <v>57.33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>38472</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45.91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>38503</v>
+      </c>
+      <c r="B65" s="2">
+        <v>89.88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>38533</v>
+      </c>
+      <c r="B66" s="2">
+        <v>96.78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>38564</v>
+      </c>
+      <c r="B67" s="2">
+        <v>105.45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>38595</v>
+      </c>
+      <c r="B68" s="2">
+        <v>105.93</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>38625</v>
+      </c>
+      <c r="B69" s="2">
+        <v>75.7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>38656</v>
+      </c>
+      <c r="B70" s="2">
+        <v>120.16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>38686</v>
+      </c>
+      <c r="B71" s="2">
+        <v>105.31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>38717</v>
+      </c>
+      <c r="B72" s="2">
+        <v>110.1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>38748</v>
+      </c>
+      <c r="B73" s="2">
+        <v>94.92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>38776</v>
+      </c>
+      <c r="B74" s="2">
+        <v>24.24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>38807</v>
+      </c>
+      <c r="B75" s="2">
+        <v>111.89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>38837</v>
+      </c>
+      <c r="B76" s="2">
+        <v>104.57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>38868</v>
+      </c>
+      <c r="B77" s="2">
+        <v>130.04</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>38898</v>
+      </c>
+      <c r="B78" s="2">
+        <v>145.03</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>38929</v>
+      </c>
+      <c r="B79" s="2">
+        <v>146.22999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>38960</v>
+      </c>
+      <c r="B80" s="2">
+        <v>187.96</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>38990</v>
+      </c>
+      <c r="B81" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>39021</v>
+      </c>
+      <c r="B82" s="2">
+        <v>238.29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>39051</v>
+      </c>
+      <c r="B83" s="2">
+        <v>229.28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>39082</v>
+      </c>
+      <c r="B84" s="2">
+        <v>209.97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>39113</v>
+      </c>
+      <c r="B85" s="2">
+        <v>158.68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>39141</v>
+      </c>
+      <c r="B86" s="2">
+        <v>237.91</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>39172</v>
+      </c>
+      <c r="B87" s="2">
+        <v>68.900000000000006</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>39202</v>
+      </c>
+      <c r="B88" s="2">
+        <v>167.34</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>39233</v>
+      </c>
+      <c r="B89" s="2">
+        <v>224.3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>39263</v>
+      </c>
+      <c r="B90" s="2">
+        <v>269.25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>39294</v>
+      </c>
+      <c r="B91" s="2">
+        <v>244.83</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>39325</v>
+      </c>
+      <c r="B92" s="2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>39355</v>
+      </c>
+      <c r="B93" s="2">
+        <v>240.88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>39386</v>
+      </c>
+      <c r="B94" s="2">
+        <v>271.98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>39416</v>
+      </c>
+      <c r="B95" s="2">
+        <v>263.89</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>39447</v>
+      </c>
+      <c r="B96" s="2">
+        <v>226.89</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>39478</v>
+      </c>
+      <c r="B97" s="2">
+        <v>194.75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>39507</v>
+      </c>
+      <c r="B98" s="2">
+        <v>82.15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>39538</v>
+      </c>
+      <c r="B99" s="2">
+        <v>131.33000000000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>39568</v>
+      </c>
+      <c r="B100" s="2">
+        <v>166.11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>39599</v>
+      </c>
+      <c r="B101" s="2">
+        <v>199.18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>39629</v>
+      </c>
+      <c r="B102" s="2">
+        <v>208.74</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>39660</v>
+      </c>
+      <c r="B103" s="2">
+        <v>254.25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>39691</v>
+      </c>
+      <c r="B104" s="2">
+        <v>293.88</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>39721</v>
+      </c>
+      <c r="B105" s="2">
+        <v>299.67</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>39752</v>
+      </c>
+      <c r="B106" s="2">
+        <v>357.84</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>39782</v>
+      </c>
+      <c r="B107" s="2">
+        <v>403.28</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>39813</v>
+      </c>
+      <c r="B108" s="2">
+        <v>390.09</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>39844</v>
+      </c>
+      <c r="B109" s="2">
+        <v>391.13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>39872</v>
+      </c>
+      <c r="B110" s="2">
+        <v>48.07</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>39903</v>
+      </c>
+      <c r="B111" s="2">
+        <v>183.68</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>39933</v>
+      </c>
+      <c r="B112" s="2">
+        <v>129.4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>39964</v>
+      </c>
+      <c r="B113" s="2">
+        <v>130.34</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>39994</v>
+      </c>
+      <c r="B114" s="2">
+        <v>79.47</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>40025</v>
+      </c>
+      <c r="B115" s="2">
+        <v>102.4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>40056</v>
+      </c>
+      <c r="B116" s="2">
+        <v>154.19999999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>40086</v>
+      </c>
+      <c r="B117" s="2">
+        <v>126.66</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>40117</v>
+      </c>
+      <c r="B118" s="2">
+        <v>237.94</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>40147</v>
+      </c>
+      <c r="B119" s="2">
+        <v>189.68</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>40178</v>
+      </c>
+      <c r="B120" s="2">
+        <v>183.91</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>40209</v>
+      </c>
+      <c r="B121" s="2">
+        <v>139.6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>40237</v>
+      </c>
+      <c r="B122" s="2">
+        <v>73.37</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>40268</v>
+      </c>
+      <c r="B123" s="2">
+        <v>-74.08</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>40298</v>
+      </c>
+      <c r="B124" s="2">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>40329</v>
+      </c>
+      <c r="B125" s="2">
+        <v>194.49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>40359</v>
+      </c>
+      <c r="B126" s="2">
+        <v>201.86</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>40390</v>
+      </c>
+      <c r="B127" s="2">
+        <v>285.44</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>40421</v>
+      </c>
+      <c r="B128" s="2">
+        <v>197.56</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>40451</v>
+      </c>
+      <c r="B129" s="2">
+        <v>165.63</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>40482</v>
+      </c>
+      <c r="B130" s="2">
+        <v>268.06</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>40512</v>
+      </c>
+      <c r="B131" s="2">
+        <v>222.94</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>40543</v>
+      </c>
+      <c r="B132" s="2">
+        <v>126.08</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>40574</v>
+      </c>
+      <c r="B133" s="2">
+        <v>57.82</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>40602</v>
+      </c>
+      <c r="B134" s="2">
+        <v>-78.73</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>40633</v>
+      </c>
+      <c r="B135" s="2">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>40663</v>
+      </c>
+      <c r="B136" s="2">
+        <v>112.22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>40694</v>
+      </c>
+      <c r="B137" s="2">
+        <v>129.29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>40724</v>
+      </c>
+      <c r="B138" s="2">
+        <v>221.93</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>40755</v>
+      </c>
+      <c r="B139" s="2">
+        <v>301.36</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>40786</v>
+      </c>
+      <c r="B140" s="2">
+        <v>178.55</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>40816</v>
+      </c>
+      <c r="B141" s="2">
+        <v>145.86000000000001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>40847</v>
+      </c>
+      <c r="B142" s="2">
+        <v>171.34</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>40877</v>
+      </c>
+      <c r="B143" s="2">
+        <v>146.63999999999999</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>40908</v>
+      </c>
+      <c r="B144" s="2">
+        <v>164.6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>40939</v>
+      </c>
+      <c r="B145" s="2">
+        <v>270.14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>40968</v>
+      </c>
+      <c r="B146" s="2">
+        <v>-320.02</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>40999</v>
+      </c>
+      <c r="B147" s="2">
+        <v>51.83</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>41029</v>
+      </c>
+      <c r="B148" s="2">
+        <v>185.55</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>41060</v>
+      </c>
+      <c r="B149" s="2">
+        <v>181.85</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>41090</v>
+      </c>
+      <c r="B150" s="2">
+        <v>316.49</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>41121</v>
+      </c>
+      <c r="B151" s="2">
+        <v>253.01</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>41152</v>
+      </c>
+      <c r="B152" s="2">
+        <v>264.18</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>41182</v>
+      </c>
+      <c r="B153" s="2">
+        <v>274.64</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>41213</v>
+      </c>
+      <c r="B154" s="2">
+        <v>320.7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>41243</v>
+      </c>
+      <c r="B155" s="2">
+        <v>194.81</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>41274</v>
+      </c>
+      <c r="B156" s="2">
+        <v>309.91000000000003</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>41305</v>
+      </c>
+      <c r="B157" s="2">
+        <v>280.89</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>41333</v>
+      </c>
+      <c r="B158" s="2">
+        <v>148.83000000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>41364</v>
+      </c>
+      <c r="B159" s="2">
+        <v>-9.06</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>41394</v>
+      </c>
+      <c r="B160" s="2">
+        <v>183.62</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>41425</v>
+      </c>
+      <c r="B161" s="2">
+        <v>206.59</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>41455</v>
+      </c>
+      <c r="B162" s="2">
+        <v>272.67</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
+        <v>41486</v>
+      </c>
+      <c r="B163" s="2">
+        <v>177.58</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="1">
+        <v>41517</v>
+      </c>
+      <c r="B164" s="2">
+        <v>281.33</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="1">
+        <v>41547</v>
+      </c>
+      <c r="B165" s="2">
+        <v>147.53</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="1">
+        <v>41578</v>
+      </c>
+      <c r="B166" s="2">
+        <v>310.35000000000002</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="1">
+        <v>41608</v>
+      </c>
+      <c r="B167" s="2">
+        <v>337.53</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
+        <v>41639</v>
+      </c>
+      <c r="B168" s="2">
+        <v>252.29</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
+        <v>41670</v>
+      </c>
+      <c r="B169" s="2">
+        <v>320.22660000000002</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="1">
+        <v>41698</v>
+      </c>
+      <c r="B170" s="2">
+        <v>-225.68969999999999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="1">
+        <v>41729</v>
+      </c>
+      <c r="B171" s="2">
+        <v>79.846500000000006</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="1">
+        <v>41759</v>
+      </c>
+      <c r="B172" s="2">
+        <v>186.63659999999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="1">
+        <v>41790</v>
+      </c>
+      <c r="B173" s="2">
+        <v>362.39389999999997</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="1">
+        <v>41820</v>
+      </c>
+      <c r="B174" s="2">
+        <v>318.94170000000003</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="1">
+        <v>41851</v>
+      </c>
+      <c r="B175" s="2">
+        <v>473.5299</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="1">
+        <v>41882</v>
+      </c>
+      <c r="B176" s="2">
+        <v>498.76119999999997</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" s="1">
+        <v>41912</v>
+      </c>
+      <c r="B177" s="2">
+        <v>312.13310000000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" s="1">
+        <v>41943</v>
+      </c>
+      <c r="B178" s="2">
+        <v>456.9939</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" s="1">
+        <v>41973</v>
+      </c>
+      <c r="B179" s="2">
+        <v>547.64559999999994</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" s="1">
+        <v>42004</v>
+      </c>
+      <c r="B180" s="2">
+        <v>499.16120000000001</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B181" s="2">
+        <v>593.14779999999996</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" s="1">
+        <v>42063</v>
+      </c>
+      <c r="B182" s="2">
+        <v>604.62099999999998</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" s="1">
+        <v>42094</v>
+      </c>
+      <c r="B183" s="2">
+        <v>25.160399999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
+        <v>42124</v>
+      </c>
+      <c r="B184" s="2">
+        <v>332.01530000000002</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
+        <v>42155</v>
+      </c>
+      <c r="B185" s="2">
+        <v>571.54570000000001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" s="1">
+        <v>42185</v>
+      </c>
+      <c r="B186" s="2">
+        <v>451.98149999999998</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" s="1">
+        <v>42216</v>
+      </c>
+      <c r="B187" s="2">
+        <v>418.6952</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" s="1">
+        <v>42247</v>
+      </c>
+      <c r="B188" s="2">
+        <v>596.88189999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>